--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleBackInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleBackInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -52,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -67,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -82,6 +96,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -97,6 +118,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -112,6 +140,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -152,6 +187,35 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1318,21 +1382,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.7272727272727" customWidth="1"/>
-    <col min="2" max="3" width="20.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="19.725" customWidth="1"/>
+    <col min="2" max="3" width="20.0916666666667" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="17.8181818181818" customWidth="1"/>
-    <col min="7" max="7" width="17.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="15.5454545454545" customWidth="1"/>
-    <col min="9" max="9" width="17.8181818181818" customWidth="1"/>
-    <col min="10" max="10" width="19.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="17.8166666666667" customWidth="1"/>
+    <col min="7" max="7" width="17.725" customWidth="1"/>
+    <col min="8" max="8" width="15.5416666666667" customWidth="1"/>
+    <col min="9" max="10" width="17.8166666666667" customWidth="1"/>
+    <col min="11" max="11" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1424,10 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleBackInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleBackInfoTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <r>
       <rPr>
@@ -228,6 +228,9 @@
       </rPr>
       <t>退回数量</t>
     </r>
+  </si>
+  <si>
+    <t>物流单号</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.725" customWidth="1"/>
@@ -1390,13 +1393,14 @@
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17.8166666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.725" customWidth="1"/>
-    <col min="8" max="8" width="15.5416666666667" customWidth="1"/>
-    <col min="9" max="10" width="17.8166666666667" customWidth="1"/>
-    <col min="11" max="11" width="19.725" customWidth="1"/>
+    <col min="7" max="7" width="17.8166666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.725" customWidth="1"/>
+    <col min="9" max="9" width="15.5416666666667" customWidth="1"/>
+    <col min="10" max="11" width="17.8166666666667" customWidth="1"/>
+    <col min="12" max="12" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,18 +1420,21 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
     </row>
